--- a/data/trans_orig/P79A6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79A6_2023-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,6%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8414</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>16879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25319</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>23143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>32717</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9449</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24486</t>
+          <t>26526</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>21807</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>52631</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>46252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>2392</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,102 +1411,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36490</t>
+          <t>40554</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31807</t>
+          <t>34931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38975</t>
+          <t>43700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>95,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>13803</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10782</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14418</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>95,74%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>74,78%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>54358</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>48601</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>58108</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>90,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>80,94%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12307</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>10068</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12857</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>95,72%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>78,31%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>48797</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>44262</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>51623</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>91,84%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>83,31%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -1524,102 +1524,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8468</t>
+          <t>10698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3636</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>25,22%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1939</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>11446</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>9,47%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>3,23%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2789</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>21,69%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>4335</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1509</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>8870</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>8,16%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>83324</t>
+          <t>99903</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>91610</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>87844</t>
+          <t>105245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>44330</t>
+          <t>52522</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38844</t>
+          <t>46783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47810</t>
+          <t>56352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>127654</t>
+          <t>152425</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118528</t>
+          <t>142160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133721</t>
+          <t>159542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>11461</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>6119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>7575</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12240</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>19037</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>11920</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>56423</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>40702</t>
+          <t>48306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54061</t>
+          <t>62902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>83459</t>
+          <t>98337</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73854</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89527</t>
+          <t>104959</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>131976</t>
+          <t>154760</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121425</t>
+          <t>140872</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141062</t>
+          <t>164572</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20653</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10138</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25811</t>
+          <t>30889</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>35613</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19957</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39594</t>
+          <t>49501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>72226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>72226</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>72226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>161019</t>
+          <t>190373</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>161019</t>
+          <t>190373</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>161019</t>
+          <t>190373</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74762</t>
+          <t>85237</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59924</t>
+          <t>74235</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>82883</t>
+          <t>93359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>86321</t>
+          <t>99740</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68999</t>
+          <t>87389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94572</t>
+          <t>107237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>30472</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>20686</t>
+          <t>19470</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38008</t>
+          <t>31821</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>119210</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>119210</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>119210</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>217248</t>
+          <t>252923</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>205983</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>225851</t>
+          <t>263429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>250988</t>
+          <t>290234</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234716</t>
+          <t>273811</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>264566</t>
+          <t>302133</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>468236</t>
+          <t>543157</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448112</t>
+          <t>522766</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>485113</t>
+          <t>560896</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>28305</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19702</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>47104</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>48905</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35327</t>
+          <t>42006</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65177</t>
+          <t>70328</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>77210</t>
+          <t>89009</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60333</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>97334</t>
+          <t>109400</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>632166</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>632166</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>632166</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
